--- a/jogos_2025-01-27.xlsx
+++ b/jogos_2025-01-27.xlsx
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,109 +1804,109 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T11" t="n">
         <v>3</v>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="M11" t="n">
-        <v>4</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R11" t="n">
+      <c r="U11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W11" t="n">
         <v>1.33</v>
       </c>
-      <c r="S11" t="n">
+      <c r="X11" t="n">
         <v>3.25</v>
       </c>
-      <c r="T11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X11" t="n">
-        <v>4.22</v>
-      </c>
       <c r="Y11" t="n">
-        <v>1.67</v>
+        <v>1.96</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.74</v>
+        <v>3.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['30', '39', '53', '69', '76']</t>
+          <t>['90+2']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['15', '20', '45+11', '58']</t>
+          <t>['29', '65']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AH11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>2.75</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45684.58333333334</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" t="n">
         <v>2</v>
       </c>
-      <c r="H12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5</v>
+        <v>1.72</v>
       </c>
       <c r="M12" t="n">
+        <v>4</v>
+      </c>
+      <c r="N12" t="n">
         <v>4.5</v>
       </c>
-      <c r="N12" t="n">
-        <v>1.55</v>
-      </c>
       <c r="O12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q12" t="n">
         <v>4.75</v>
       </c>
-      <c r="P12" t="n">
+      <c r="R12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T12" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X12" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>['30', '39', '53', '69', '76']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>['15', '20', '45+11', '58']</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH12" t="n">
         <v>2.2</v>
       </c>
-      <c r="U12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X12" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>['2', '90+3']</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>['50']</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AI12" t="n">
-        <v>3</v>
+        <v>1.44</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.36</v>
+        <v>2.75</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45684.58333333334</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,109 +2062,109 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
       </c>
       <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>5</v>
+      </c>
+      <c r="M13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q13" t="n">
         <v>2</v>
       </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
+      <c r="R13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X13" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y13" t="n">
         <v>1.5</v>
       </c>
-      <c r="M13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>5</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="P13" t="n">
+      <c r="Z13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>['2', '90+3']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>['50']</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q13" t="n">
-        <v>5</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X13" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>['10', '35', '81']</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>['19']</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AH13" t="n">
-        <v>2.9</v>
+        <v>1.15</v>
       </c>
       <c r="AI13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>3.2</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45684.58333333334</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,22 +2191,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2217,65 +2217,65 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.2</v>
+        <v>1.33</v>
       </c>
       <c r="M14" t="n">
-        <v>2.6</v>
+        <v>4.33</v>
       </c>
       <c r="N14" t="n">
-        <v>2.05</v>
+        <v>7.5</v>
       </c>
       <c r="O14" t="n">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="P14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="T14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['83']</t>
+          <t>['45+1', '64']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.7</v>
+        <v>1.09</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.18</v>
+        <v>2.9</v>
       </c>
       <c r="AI14" t="n">
-        <v>3.2</v>
+        <v>1.25</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.73</v>
+        <v>4</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45684.58333333334</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="M15" t="n">
-        <v>4.33</v>
+        <v>2.9</v>
       </c>
       <c r="N15" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="P15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC15" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="AD15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>['22', '54']</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>['28']</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>3.25</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X15" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>['45+1', '64']</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>4</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45684.58333333334</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,109 +2449,109 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Ironi Ramat HaSharon</t>
         </is>
       </c>
       <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>1</v>
       </c>
-      <c r="H16" t="n">
-        <v>2</v>
-      </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>0</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="M16" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="W16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X16" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['24', '78']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>2.1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>['90+2']</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>['29', '65']</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>2.2</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45684.58333333334</v>
@@ -2578,48 +2578,48 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ironi Ramat HaSharon</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
         <v>2</v>
       </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="N17" t="n">
-        <v>2.63</v>
+        <v>5</v>
       </c>
       <c r="O17" t="n">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="P17" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
         <v>1.33</v>
@@ -2634,7 +2634,7 @@
         <v>1.5</v>
       </c>
       <c r="V17" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="W17" t="n">
         <v>1.22</v>
@@ -2643,44 +2643,44 @@
         <v>4</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['24', '78']</t>
+          <t>['10', '35', '81']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.43</v>
+        <v>1.09</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.53</v>
+        <v>2.9</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45684.58333333334</v>
@@ -2707,25 +2707,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.83</v>
+        <v>4.2</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="N18" t="n">
-        <v>4.5</v>
+        <v>2.05</v>
       </c>
       <c r="O18" t="n">
+        <v>5</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC18" t="n">
         <v>2.63</v>
       </c>
-      <c r="P18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AD18" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['22', '54']</t>
+          <t>['83']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['28']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.13</v>
+        <v>1.7</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.93</v>
+        <v>1.18</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.57</v>
+        <v>3.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>3.25</v>
+        <v>1.73</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45684.58333333334</v>
@@ -3352,109 +3352,109 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
         <v>2</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>0</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X23" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>['79']</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>['12', '63']</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="M23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N23" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>5</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X23" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>['2', '43']</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>3</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45684.66666666666</v>
@@ -3481,109 +3481,109 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
         <v>2</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>0</v>
       </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="M24" t="n">
-        <v>3.77</v>
+        <v>3.9</v>
       </c>
       <c r="N24" t="n">
-        <v>2.68</v>
+        <v>5.25</v>
       </c>
       <c r="O24" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="P24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T24" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.2</v>
-      </c>
       <c r="U24" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W24" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X24" t="n">
-        <v>6</v>
+        <v>4.33</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.72</v>
+        <v>1.47</v>
       </c>
       <c r="AC24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>['2', '43']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AI24" t="n">
         <v>1.4</v>
       </c>
-      <c r="AD24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>['79']</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>['12', '63']</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AJ24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45684.66666666666</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,25 +3610,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="N25" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="O25" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="P25" t="n">
         <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S25" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="T25" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U25" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V25" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W25" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X25" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['84', '89']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2', '66', '73', '82']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.79</v>
+        <v>2.07</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45684.6875</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,22 +3739,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G26" t="n">
+        <v>3</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
         <v>2</v>
-      </c>
-      <c r="H26" t="n">
-        <v>4</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W26" t="n">
         <v>1.5</v>
       </c>
-      <c r="M26" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.35</v>
-      </c>
       <c r="X26" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.78</v>
+        <v>4.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['84', '89']</t>
+          <t>['5', '27', '75']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['2', '66', '73', '82']</t>
+          <t>['44']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.07</v>
+        <v>1.72</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45684.6875</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,106 +3997,106 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>5</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V28" t="n">
         <v>1</v>
       </c>
-      <c r="I28" t="n">
-        <v>2</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L28" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="M28" t="n">
-        <v>3</v>
-      </c>
-      <c r="N28" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O28" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P28" t="n">
+      <c r="W28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC28" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q28" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R28" t="n">
+      <c r="AD28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AI28" t="n">
         <v>1.57</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>['5', '27', '75']</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>['44']</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1.67</v>
       </c>
       <c r="AJ28" t="n">
         <v>2.88</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,25 +4126,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
         <v>2</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="M29" t="n">
         <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="O29" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P29" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="S29" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="T29" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U29" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V29" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="W29" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="X29" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AA29" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AC29" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['61', '84']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27', '64']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45684.69791666666</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,25 +4255,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" t="n">
         <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>2</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="M30" t="n">
         <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="O30" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P30" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="R30" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="S30" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="T30" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U30" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V30" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="W30" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="X30" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="Y30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC30" t="n">
         <v>2</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AD30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>['61', '84']</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI30" t="n">
         <v>1.73</v>
       </c>
-      <c r="AA30" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>['27', '64']</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AJ30" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45684.69791666666</v>
